--- a/data/dividends_info_20260309.xlsx
+++ b/data/dividends_info_20260309.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.25</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.365853658536585</v>
+        <v>1.380670590663352</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21.54999923706055</v>
+        <v>21.46999931335449</v>
       </c>
       <c r="I3" t="n">
-        <v>3.944315684885106</v>
+        <v>3.959012702302668</v>
       </c>
       <c r="J3" t="n">
         <v>105</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.486000061035156</v>
+        <v>6.455999851226807</v>
       </c>
       <c r="I4" t="n">
-        <v>2.795251284210823</v>
+        <v>2.808240461243944</v>
       </c>
       <c r="J4" t="n">
         <v>105</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.52000045776367</v>
+        <v>10.4350004196167</v>
       </c>
       <c r="I5" t="n">
-        <v>2.756653872443346</v>
+        <v>2.779108656812611</v>
       </c>
       <c r="J5" t="n">
         <v>70</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32.97999954223633</v>
+        <v>32.40000152587891</v>
       </c>
       <c r="I6" t="n">
-        <v>6.064281466828616</v>
+        <v>6.172839215462804</v>
       </c>
       <c r="J6" t="n">
         <v>70</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.047999858856201</v>
+        <v>3.875999927520752</v>
       </c>
       <c r="I7" t="n">
-        <v>2.470355817360525</v>
+        <v>2.579979408409435</v>
       </c>
       <c r="J7" t="n">
         <v>70</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>75.04000091552734</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.385927488421448</v>
+        <v>1.440842332506093</v>
       </c>
       <c r="J8" t="n">
         <v>70</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.25</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>4.292682926829269</v>
+        <v>4.339250427799106</v>
       </c>
       <c r="J9" t="n">
         <v>70</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.1200008392334</v>
+        <v>19.21500015258789</v>
       </c>
       <c r="I10" t="n">
-        <v>4.131798981823028</v>
+        <v>4.111371291837342</v>
       </c>
       <c r="J10" t="n">
         <v>70</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.203999996185303</v>
+        <v>5.204999923706055</v>
       </c>
       <c r="I11" t="n">
-        <v>3.651037666012222</v>
+        <v>3.65033626868368</v>
       </c>
       <c r="J11" t="n">
         <v>70</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.42000007629395</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I12" t="n">
-        <v>4.145873290181859</v>
+        <v>4.173912889640444</v>
       </c>
       <c r="J12" t="n">
         <v>70</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24.92000007629395</v>
+        <v>24.6200008392334</v>
       </c>
       <c r="I13" t="n">
-        <v>1.765650074851187</v>
+        <v>1.787164845660096</v>
       </c>
       <c r="J13" t="n">
         <v>70</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
+        <v>54.27999877929688</v>
       </c>
       <c r="I14" t="n">
-        <v>2.545454545454545</v>
+        <v>2.579218923147763</v>
       </c>
       <c r="J14" t="n">
         <v>70</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.785000085830688</v>
+        <v>2.871000051498413</v>
       </c>
       <c r="I15" t="n">
-        <v>10.77199248669029</v>
+        <v>10.44932060671423</v>
       </c>
       <c r="J15" t="n">
         <v>70</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22.61000061035156</v>
+        <v>22.76000022888184</v>
       </c>
       <c r="I16" t="n">
-        <v>2.653692984534026</v>
+        <v>2.636203839921829</v>
       </c>
       <c r="J16" t="n">
         <v>70</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8.470000267028809</v>
+        <v>8.260000228881836</v>
       </c>
       <c r="I17" t="n">
-        <v>6.027154473503674</v>
+        <v>6.180387237944506</v>
       </c>
       <c r="J17" t="n">
         <v>56</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18.79999923706055</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="I18" t="n">
-        <v>3.989361864023487</v>
+        <v>4.098360826601157</v>
       </c>
       <c r="J18" t="n">
         <v>56</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.934999942779541</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I19" t="n">
-        <v>3.811944146917711</v>
+        <v>3.978779860978569</v>
       </c>
       <c r="J19" t="n">
         <v>56</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="I20" t="n">
-        <v>1.643075</v>
+        <v>1.676607110225773</v>
       </c>
       <c r="J20" t="n">
         <v>56</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>25.14999961853027</v>
+        <v>25.25</v>
       </c>
       <c r="I21" t="n">
-        <v>4.373757521608592</v>
+        <v>4.356435643564357</v>
       </c>
       <c r="J21" t="n">
         <v>56</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.214999914169312</v>
+        <v>2.194999933242798</v>
       </c>
       <c r="I22" t="n">
-        <v>2.93453735976224</v>
+        <v>2.961275716485869</v>
       </c>
       <c r="J22" t="n">
         <v>49</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.71999979019165</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="I23" t="n">
-        <v>7.440476422778882</v>
+        <v>7.656967594717345</v>
       </c>
       <c r="J23" t="n">
         <v>42</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>11.46000003814697</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="I24" t="n">
-        <v>4.712041869131752</v>
+        <v>4.753521270421833</v>
       </c>
       <c r="J24" t="n">
         <v>42</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.375999927520752</v>
+        <v>6.334000110626221</v>
       </c>
       <c r="I25" t="n">
-        <v>1.568381448192457</v>
+        <v>1.578781153354185</v>
       </c>
       <c r="J25" t="n">
         <v>42</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>301.6000061035156</v>
+        <v>295</v>
       </c>
       <c r="I26" t="n">
-        <v>1.19860740279934</v>
+        <v>1.225423728813559</v>
       </c>
       <c r="J26" t="n">
         <v>42</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.60000038146973</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I27" t="n">
-        <v>5.112781881564981</v>
+        <v>5.250965328304414</v>
       </c>
       <c r="J27" t="n">
         <v>42</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>13.75</v>
+        <v>13.40999984741211</v>
       </c>
       <c r="I28" t="n">
-        <v>4.254545454545455</v>
+        <v>4.36241615702102</v>
       </c>
       <c r="J28" t="n">
         <v>42</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>15.72000026702881</v>
+        <v>15.38500022888184</v>
       </c>
       <c r="I29" t="n">
-        <v>4.00763351971033</v>
+        <v>4.094897566639736</v>
       </c>
       <c r="J29" t="n">
         <v>42</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>99.09999847412109</v>
+        <v>97.01999664306641</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9081735760420071</v>
+        <v>0.9276438168835157</v>
       </c>
       <c r="J30" t="n">
         <v>42</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>66.12000274658203</v>
+        <v>65.08999633789062</v>
       </c>
       <c r="I31" t="n">
-        <v>2.602540726737877</v>
+        <v>2.643724223100434</v>
       </c>
       <c r="J31" t="n">
         <v>42</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>25.39999961853027</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5511811106401145</v>
+        <v>0.5907172805619613</v>
       </c>
       <c r="J32" t="n">
         <v>35</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>20.52499961853027</v>
+        <v>20.9950008392334</v>
       </c>
       <c r="I34" t="n">
-        <v>1.266747891996393</v>
+        <v>1.238390043377076</v>
       </c>
       <c r="J34" t="n">
         <v>14</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>27.14500045776367</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3315527665583786</v>
+        <v>0.3251445050857577</v>
       </c>
       <c r="J35" t="n">
         <v>14</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>51.25</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I36" t="n">
-        <v>1.268292682926829</v>
+        <v>1.282051262758827</v>
       </c>
       <c r="J36" t="n">
         <v>-14</v>
@@ -3064,7 +3064,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3380,14 +3380,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3431,14 +3431,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3686,14 +3686,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3703,14 +3703,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3720,14 +3720,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3805,14 +3805,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3907,14 +3907,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3924,14 +3924,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4043,14 +4043,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4094,14 +4094,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4128,14 +4128,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4196,14 +4196,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4305,7 +4305,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4434,14 +4434,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4519,14 +4519,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4832,7 +4832,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5053,7 +5053,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5121,7 +5121,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5138,7 +5138,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5189,7 +5189,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5335,14 +5335,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5420,14 +5420,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5454,14 +5454,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5573,14 +5573,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5597,7 +5597,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5614,7 +5614,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5665,7 +5665,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5767,7 +5767,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5801,7 +5801,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5845,14 +5845,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5869,7 +5869,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5896,14 +5896,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5920,7 +5920,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5964,14 +5964,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5988,7 +5988,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6056,7 +6056,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6083,14 +6083,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6107,7 +6107,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6117,14 +6117,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6134,14 +6134,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6158,7 +6158,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6192,7 +6192,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6209,7 +6209,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6226,7 +6226,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6253,14 +6253,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6294,7 +6294,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6311,7 +6311,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6328,7 +6328,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6362,7 +6362,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6447,7 +6447,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,7 +6532,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6549,7 +6549,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6583,7 +6583,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6600,7 +6600,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6617,7 +6617,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6634,7 +6634,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6651,7 +6651,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6685,7 +6685,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6712,14 +6712,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6753,7 +6753,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6763,14 +6763,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6787,7 +6787,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6838,7 +6838,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6872,7 +6872,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6889,7 +6889,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6906,7 +6906,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6933,14 +6933,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6950,14 +6950,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6974,7 +6974,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7025,7 +7025,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7042,7 +7042,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7059,7 +7059,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7076,7 +7076,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7093,7 +7093,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7110,7 +7110,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7127,7 +7127,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7144,7 +7144,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7154,14 +7154,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7188,14 +7188,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7212,7 +7212,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7229,7 +7229,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7263,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7280,7 +7280,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7290,14 +7290,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7314,7 +7314,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7331,7 +7331,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7348,7 +7348,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7399,7 +7399,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7433,7 +7433,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7450,7 +7450,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7467,7 +7467,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7518,7 +7518,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7535,7 +7535,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7552,7 +7552,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7562,14 +7562,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7586,7 +7586,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7596,14 +7596,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7620,7 +7620,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7637,7 +7637,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7654,7 +7654,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7671,7 +7671,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7688,7 +7688,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7705,7 +7705,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7739,7 +7739,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7773,7 +7773,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7790,7 +7790,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7807,7 +7807,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7841,7 +7841,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7858,7 +7858,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7875,7 +7875,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7892,7 +7892,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7909,7 +7909,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7936,14 +7936,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7977,7 +7977,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7994,7 +7994,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8011,7 +8011,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8021,14 +8021,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -8062,7 +8062,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8113,7 +8113,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8130,7 +8130,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8147,7 +8147,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8164,7 +8164,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8181,7 +8181,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8198,7 +8198,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8215,7 +8215,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8249,7 +8249,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8266,7 +8266,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8283,7 +8283,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8300,7 +8300,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8317,7 +8317,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8327,14 +8327,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8351,7 +8351,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8368,7 +8368,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8385,7 +8385,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8402,7 +8402,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8419,7 +8419,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8429,14 +8429,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8497,14 +8497,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8555,7 +8555,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -8565,14 +8565,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8597,146 +8597,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001031084</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2027-02-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2027-02-24</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.365853658536585</v>
-      </c>
-      <c r="I2" t="n">
-        <v>350</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005253205</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>25.14999961853027</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4.373757521608592</v>
-      </c>
-      <c r="I3" t="n">
-        <v>56</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8747,61 +8610,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>